--- a/output/Data and Chart Outputs/india_gas.xlsx
+++ b/output/Data and Chart Outputs/india_gas.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Supply" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sectoral" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sectoral RLNG" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LNG imports" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chart - Supply" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sectoral" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sectoral RLNG" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="LNG imports" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -148,17 +148,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>India gas consumption by sector (PPAC) (to Aug/26)</a:t>
             </a:r>
           </a:p>
@@ -179,10 +180,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -207,10 +208,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -235,10 +236,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -263,10 +264,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -291,10 +292,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9A9A9A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -327,8 +328,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -354,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -372,7 +373,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -386,7 +387,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -395,17 +396,18 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>India gas supply: domestic production and LNG imports (PPAC) (to Aug/26)</a:t>
             </a:r>
           </a:p>
@@ -426,10 +428,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -454,10 +456,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -490,8 +492,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -517,8 +519,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -535,7 +537,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -549,7 +551,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -558,7 +560,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -573,9 +575,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -585,7 +587,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -600,9 +602,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
